--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1306"/>
+  <dimension ref="A1:G1307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32061,6 +32061,22 @@
         <v>1569.17</v>
       </c>
     </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1307" t="n">
+        <v>1380.3</v>
+      </c>
+      <c r="C1307" t="n">
+        <v>885.29</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>1584.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1307"/>
+  <dimension ref="A1:G1308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32012,6 +32012,15 @@
       <c r="D1303" t="n">
         <v>1560.81</v>
       </c>
+      <c r="E1303" t="n">
+        <v>118.6923</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>154.42</v>
+      </c>
+      <c r="G1303" t="n">
+        <v>1.1549</v>
+      </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
@@ -32028,6 +32037,15 @@
       <c r="D1304" t="n">
         <v>1554.09</v>
       </c>
+      <c r="E1304" t="n">
+        <v>118.8822</v>
+      </c>
+      <c r="F1304" t="n">
+        <v>155.11</v>
+      </c>
+      <c r="G1304" t="n">
+        <v>1.1542</v>
+      </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
@@ -32044,6 +32062,15 @@
       <c r="D1305" t="n">
         <v>1561.44</v>
       </c>
+      <c r="E1305" t="n">
+        <v>118.9206</v>
+      </c>
+      <c r="F1305" t="n">
+        <v>155.08</v>
+      </c>
+      <c r="G1305" t="n">
+        <v>1.1538</v>
+      </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
@@ -32060,6 +32087,15 @@
       <c r="D1306" t="n">
         <v>1569.17</v>
       </c>
+      <c r="E1306" t="n">
+        <v>119.3489</v>
+      </c>
+      <c r="F1306" t="n">
+        <v>155.85</v>
+      </c>
+      <c r="G1306" t="n">
+        <v>1.1479</v>
+      </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
@@ -32075,6 +32111,31 @@
       </c>
       <c r="D1307" t="n">
         <v>1584.31</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>119.5133</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>156.87</v>
+      </c>
+      <c r="G1307" t="n">
+        <v>1.1464</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1308" t="n">
+        <v>1383.8</v>
+      </c>
+      <c r="C1308" t="n">
+        <v>881.01</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>1588.6</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1308"/>
+  <dimension ref="A1:G1309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32138,6 +32138,22 @@
         <v>1588.6</v>
       </c>
     </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1309" t="n">
+        <v>1384.3</v>
+      </c>
+      <c r="C1309" t="n">
+        <v>879.84</v>
+      </c>
+      <c r="D1309" t="n">
+        <v>1587.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1309"/>
+  <dimension ref="A1:G1310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32154,6 +32154,22 @@
         <v>1587.1</v>
       </c>
     </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1310" t="n">
+        <v>1360</v>
+      </c>
+      <c r="C1310" t="n">
+        <v>863.6799999999999</v>
+      </c>
+      <c r="D1310" t="n">
+        <v>1556.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1310"/>
+  <dimension ref="A1:G1313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32137,6 +32137,15 @@
       <c r="D1308" t="n">
         <v>1588.6</v>
       </c>
+      <c r="E1308" t="n">
+        <v>119.4014</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>157.46</v>
+      </c>
+      <c r="G1308" t="n">
+        <v>1.1469</v>
+      </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
@@ -32153,6 +32162,15 @@
       <c r="D1309" t="n">
         <v>1587.1</v>
       </c>
+      <c r="E1309" t="n">
+        <v>119.5933</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>157.55</v>
+      </c>
+      <c r="G1309" t="n">
+        <v>1.1432</v>
+      </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
@@ -32168,6 +32186,63 @@
       </c>
       <c r="D1310" t="n">
         <v>1556.93</v>
+      </c>
+      <c r="E1310" t="n">
+        <v>120.1169</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="G1310" t="n">
+        <v>1.1394</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E1311" t="n">
+        <v>120.5521</v>
+      </c>
+      <c r="F1311" t="n">
+        <v>158.92</v>
+      </c>
+      <c r="G1311" t="n">
+        <v>1.1373</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E1312" t="n">
+        <v>120.33</v>
+      </c>
+      <c r="F1312" t="n">
+        <v>157.18</v>
+      </c>
+      <c r="G1312" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1313" t="n">
+        <v>1352</v>
+      </c>
+      <c r="C1313" t="n">
+        <v>857.9</v>
+      </c>
+      <c r="D1313" t="n">
+        <v>1538.04</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1313"/>
+  <dimension ref="A1:G1314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32245,6 +32245,22 @@
         <v>1538.04</v>
       </c>
     </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1314" t="n">
+        <v>1360</v>
+      </c>
+      <c r="C1314" t="n">
+        <v>863.9</v>
+      </c>
+      <c r="D1314" t="n">
+        <v>1546.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1314"/>
+  <dimension ref="A1:G1315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32261,6 +32261,22 @@
         <v>1546.46</v>
       </c>
     </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1315" t="n">
+        <v>1358.4</v>
+      </c>
+      <c r="C1315" t="n">
+        <v>863.16</v>
+      </c>
+      <c r="D1315" t="n">
+        <v>1540.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1315"/>
+  <dimension ref="A1:G1316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32277,6 +32277,22 @@
         <v>1540.29</v>
       </c>
     </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1316" t="n">
+        <v>1355.7</v>
+      </c>
+      <c r="C1316" t="n">
+        <v>861.28</v>
+      </c>
+      <c r="D1316" t="n">
+        <v>1536.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1316"/>
+  <dimension ref="A1:G1317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32293,6 +32293,22 @@
         <v>1536.14</v>
       </c>
     </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1317" t="n">
+        <v>1359.6</v>
+      </c>
+      <c r="C1317" t="n">
+        <v>860.3200000000001</v>
+      </c>
+      <c r="D1317" t="n">
+        <v>1528.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -32244,6 +32244,15 @@
       <c r="D1313" t="n">
         <v>1538.04</v>
       </c>
+      <c r="E1313" t="n">
+        <v>120.6958</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>157.44</v>
+      </c>
+      <c r="G1313" t="n">
+        <v>1.1367</v>
+      </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
@@ -32260,6 +32269,15 @@
       <c r="D1314" t="n">
         <v>1546.46</v>
       </c>
+      <c r="E1314" t="n">
+        <v>121.0296</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="G1314" t="n">
+        <v>1.1336</v>
+      </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
@@ -32276,6 +32294,15 @@
       <c r="D1315" t="n">
         <v>1540.29</v>
       </c>
+      <c r="E1315" t="n">
+        <v>120.9693</v>
+      </c>
+      <c r="F1315" t="n">
+        <v>157.25</v>
+      </c>
+      <c r="G1315" t="n">
+        <v>1.1345</v>
+      </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
@@ -32292,6 +32319,15 @@
       <c r="D1316" t="n">
         <v>1536.14</v>
       </c>
+      <c r="E1316" t="n">
+        <v>121.7882</v>
+      </c>
+      <c r="F1316" t="n">
+        <v>157.63</v>
+      </c>
+      <c r="G1316" t="n">
+        <v>1.1232</v>
+      </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
@@ -32307,6 +32343,15 @@
       </c>
       <c r="D1317" t="n">
         <v>1528.67</v>
+      </c>
+      <c r="E1317" t="n">
+        <v>121.3848</v>
+      </c>
+      <c r="F1317" t="n">
+        <v>157.81</v>
+      </c>
+      <c r="G1317" t="n">
+        <v>1.1259</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1317"/>
+  <dimension ref="A1:G1318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32354,6 +32354,22 @@
         <v>1.1259</v>
       </c>
     </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1318" t="n">
+        <v>1358.5</v>
+      </c>
+      <c r="C1318" t="n">
+        <v>860.16</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>1524.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1318"/>
+  <dimension ref="A1:G1319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32370,6 +32370,22 @@
         <v>1524.1</v>
       </c>
     </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B1319" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="C1319" t="n">
+        <v>849.1</v>
+      </c>
+      <c r="D1319" t="n">
+        <v>1512.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1319"/>
+  <dimension ref="A1:G1320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32386,6 +32386,22 @@
         <v>1512.27</v>
       </c>
     </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B1320" t="n">
+        <v>1339.2</v>
+      </c>
+      <c r="C1320" t="n">
+        <v>847.46</v>
+      </c>
+      <c r="D1320" t="n">
+        <v>1500.04</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1320"/>
+  <dimension ref="A1:G1321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32402,6 +32402,22 @@
         <v>1500.04</v>
       </c>
     </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1321" t="n">
+        <v>1338</v>
+      </c>
+      <c r="C1321" t="n">
+        <v>845.42</v>
+      </c>
+      <c r="D1321" t="n">
+        <v>1498.43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1321"/>
+  <dimension ref="A1:G1322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32418,6 +32418,22 @@
         <v>1498.43</v>
       </c>
     </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1322" t="n">
+        <v>1335.8</v>
+      </c>
+      <c r="C1322" t="n">
+        <v>842.3</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>1490.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1322"/>
+  <dimension ref="A1:G1324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32357,80 +32357,139 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B1318" t="n">
-        <v>1358.5</v>
-      </c>
-      <c r="C1318" t="n">
-        <v>860.16</v>
-      </c>
-      <c r="D1318" t="n">
-        <v>1524.1</v>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E1318" t="n">
+        <v>121.2708</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>157.97</v>
+      </c>
+      <c r="G1318" t="n">
+        <v>1.1211</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B1319" t="n">
-        <v>1343.4</v>
+        <v>1358.5</v>
       </c>
       <c r="C1319" t="n">
-        <v>849.1</v>
+        <v>860.16</v>
       </c>
       <c r="D1319" t="n">
-        <v>1512.27</v>
+        <v>1524.1</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>120.8976</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>158.12</v>
+      </c>
+      <c r="G1319" t="n">
+        <v>1.1262</v>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>1339.2</v>
+        <v>1343.4</v>
       </c>
       <c r="C1320" t="n">
-        <v>847.46</v>
+        <v>849.1</v>
       </c>
       <c r="D1320" t="n">
-        <v>1500.04</v>
+        <v>1512.27</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>121.2558</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>158.11</v>
+      </c>
+      <c r="G1320" t="n">
+        <v>1.1187</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B1321" t="n">
-        <v>1338</v>
+        <v>1339.2</v>
       </c>
       <c r="C1321" t="n">
-        <v>845.42</v>
+        <v>847.46</v>
       </c>
       <c r="D1321" t="n">
-        <v>1498.43</v>
+        <v>1500.04</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>121.4469</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>158.33</v>
+      </c>
+      <c r="G1321" t="n">
+        <v>1.1192</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E1322" t="n">
+        <v>121.6023</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>158.34</v>
+      </c>
+      <c r="G1322" t="n">
+        <v>1.1193</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1323" t="n">
+        <v>1338</v>
+      </c>
+      <c r="C1323" t="n">
+        <v>845.42</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>1498.43</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B1322" t="n">
+      <c r="B1324" t="n">
         <v>1335.8</v>
       </c>
-      <c r="C1322" t="n">
+      <c r="C1324" t="n">
         <v>842.3</v>
       </c>
-      <c r="D1322" t="n">
+      <c r="D1324" t="n">
         <v>1490.42</v>
       </c>
     </row>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1324"/>
+  <dimension ref="A1:G1325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32493,6 +32493,22 @@
         <v>1490.42</v>
       </c>
     </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1325" t="n">
+        <v>1340.5</v>
+      </c>
+      <c r="C1325" t="n">
+        <v>846.5700000000001</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>1500.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1325"/>
+  <dimension ref="A1:G1326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32509,6 +32509,22 @@
         <v>1500.96</v>
       </c>
     </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1326" t="n">
+        <v>1338.6</v>
+      </c>
+      <c r="C1326" t="n">
+        <v>846.65</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>1495.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1326"/>
+  <dimension ref="A1:G1327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32525,6 +32525,22 @@
         <v>1495.48</v>
       </c>
     </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1327" t="n">
+        <v>1348.5</v>
+      </c>
+      <c r="C1327" t="n">
+        <v>853.02</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>1512.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1327"/>
+  <dimension ref="A1:G1328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32492,6 +32492,15 @@
       <c r="D1324" t="n">
         <v>1490.42</v>
       </c>
+      <c r="E1324" t="n">
+        <v>121.4433</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>158.36</v>
+      </c>
+      <c r="G1324" t="n">
+        <v>1.1196</v>
+      </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
@@ -32508,6 +32517,15 @@
       <c r="D1325" t="n">
         <v>1500.96</v>
       </c>
+      <c r="E1325" t="n">
+        <v>122.0037</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>158.84</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>1.1123</v>
+      </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
@@ -32524,6 +32542,15 @@
       <c r="D1326" t="n">
         <v>1495.48</v>
       </c>
+      <c r="E1326" t="n">
+        <v>121.5693</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>158.18</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>1.1204</v>
+      </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
@@ -32539,6 +32566,31 @@
       </c>
       <c r="D1327" t="n">
         <v>1512.14</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>121.4048</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>158</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>1.1231</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1328" t="n">
+        <v>1342.4</v>
+      </c>
+      <c r="C1328" t="n">
+        <v>850.24</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>1505.17</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1328"/>
+  <dimension ref="A1:G1326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32464,133 +32464,65 @@
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B1323" t="n">
-        <v>1338</v>
-      </c>
-      <c r="C1323" t="n">
-        <v>845.42</v>
-      </c>
-      <c r="D1323" t="n">
-        <v>1498.43</v>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E1323" t="n">
+        <v>121.4433</v>
+      </c>
+      <c r="F1323" t="n">
+        <v>158.36</v>
+      </c>
+      <c r="G1323" t="n">
+        <v>1.1196</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B1324" t="n">
-        <v>1335.8</v>
-      </c>
-      <c r="C1324" t="n">
-        <v>842.3</v>
-      </c>
-      <c r="D1324" t="n">
-        <v>1490.42</v>
+          <t>2026-10-14</t>
+        </is>
       </c>
       <c r="E1324" t="n">
-        <v>121.4433</v>
+        <v>122.0037</v>
       </c>
       <c r="F1324" t="n">
-        <v>158.36</v>
+        <v>158.84</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.1196</v>
+        <v>1.1123</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B1325" t="n">
-        <v>1340.5</v>
-      </c>
-      <c r="C1325" t="n">
-        <v>846.5700000000001</v>
-      </c>
-      <c r="D1325" t="n">
-        <v>1500.96</v>
+          <t>2026-10-15</t>
+        </is>
       </c>
       <c r="E1325" t="n">
-        <v>122.0037</v>
+        <v>121.5693</v>
       </c>
       <c r="F1325" t="n">
-        <v>158.84</v>
+        <v>158.18</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.1123</v>
+        <v>1.1204</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B1326" t="n">
-        <v>1338.6</v>
-      </c>
-      <c r="C1326" t="n">
-        <v>846.65</v>
-      </c>
-      <c r="D1326" t="n">
-        <v>1495.48</v>
+          <t>2026-10-16</t>
+        </is>
       </c>
       <c r="E1326" t="n">
-        <v>121.5693</v>
+        <v>121.4048</v>
       </c>
       <c r="F1326" t="n">
-        <v>158.18</v>
+        <v>158</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.1204</v>
-      </c>
-    </row>
-    <row r="1327">
-      <c r="A1327" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B1327" t="n">
-        <v>1348.5</v>
-      </c>
-      <c r="C1327" t="n">
-        <v>853.02</v>
-      </c>
-      <c r="D1327" t="n">
-        <v>1512.14</v>
-      </c>
-      <c r="E1327" t="n">
-        <v>121.4048</v>
-      </c>
-      <c r="F1327" t="n">
-        <v>158</v>
-      </c>
-      <c r="G1327" t="n">
         <v>1.1231</v>
-      </c>
-    </row>
-    <row r="1328">
-      <c r="A1328" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B1328" t="n">
-        <v>1342.4</v>
-      </c>
-      <c r="C1328" t="n">
-        <v>850.24</v>
-      </c>
-      <c r="D1328" t="n">
-        <v>1505.17</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1326"/>
+  <dimension ref="A1:G1328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32357,172 +32357,177 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E1318" t="n">
-        <v>121.2708</v>
-      </c>
-      <c r="F1318" t="n">
-        <v>157.97</v>
-      </c>
-      <c r="G1318" t="n">
-        <v>1.1211</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1318" t="n">
+        <v>1358.5</v>
+      </c>
+      <c r="C1318" t="n">
+        <v>860.16</v>
+      </c>
+      <c r="D1318" t="n">
+        <v>1524.1</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B1319" t="n">
-        <v>1358.5</v>
+        <v>1343.4</v>
       </c>
       <c r="C1319" t="n">
-        <v>860.16</v>
+        <v>849.1</v>
       </c>
       <c r="D1319" t="n">
-        <v>1524.1</v>
-      </c>
-      <c r="E1319" t="n">
-        <v>120.8976</v>
-      </c>
-      <c r="F1319" t="n">
-        <v>158.12</v>
-      </c>
-      <c r="G1319" t="n">
-        <v>1.1262</v>
+        <v>1512.27</v>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>1343.4</v>
+        <v>1339.2</v>
       </c>
       <c r="C1320" t="n">
-        <v>849.1</v>
+        <v>847.46</v>
       </c>
       <c r="D1320" t="n">
-        <v>1512.27</v>
-      </c>
-      <c r="E1320" t="n">
-        <v>121.2558</v>
-      </c>
-      <c r="F1320" t="n">
-        <v>158.11</v>
-      </c>
-      <c r="G1320" t="n">
-        <v>1.1187</v>
+        <v>1500.04</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B1321" t="n">
-        <v>1339.2</v>
+        <v>1338</v>
       </c>
       <c r="C1321" t="n">
-        <v>847.46</v>
+        <v>845.42</v>
       </c>
       <c r="D1321" t="n">
-        <v>1500.04</v>
-      </c>
-      <c r="E1321" t="n">
-        <v>121.4469</v>
-      </c>
-      <c r="F1321" t="n">
-        <v>158.33</v>
-      </c>
-      <c r="G1321" t="n">
-        <v>1.1192</v>
+        <v>1498.43</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="E1322" t="n">
-        <v>121.6023</v>
-      </c>
-      <c r="F1322" t="n">
-        <v>158.34</v>
-      </c>
-      <c r="G1322" t="n">
-        <v>1.1193</v>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1322" t="n">
+        <v>1335.8</v>
+      </c>
+      <c r="C1322" t="n">
+        <v>842.3</v>
+      </c>
+      <c r="D1322" t="n">
+        <v>1490.42</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="E1323" t="n">
-        <v>121.4433</v>
-      </c>
-      <c r="F1323" t="n">
-        <v>158.36</v>
-      </c>
-      <c r="G1323" t="n">
-        <v>1.1196</v>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1323" t="n">
+        <v>1340.5</v>
+      </c>
+      <c r="C1323" t="n">
+        <v>846.5700000000001</v>
+      </c>
+      <c r="D1323" t="n">
+        <v>1500.96</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="E1324" t="n">
-        <v>122.0037</v>
-      </c>
-      <c r="F1324" t="n">
-        <v>158.84</v>
-      </c>
-      <c r="G1324" t="n">
-        <v>1.1123</v>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B1324" t="n">
+        <v>1338.6</v>
+      </c>
+      <c r="C1324" t="n">
+        <v>846.65</v>
+      </c>
+      <c r="D1324" t="n">
+        <v>1495.48</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="E1325" t="n">
-        <v>121.5693</v>
-      </c>
-      <c r="F1325" t="n">
-        <v>158.18</v>
-      </c>
-      <c r="G1325" t="n">
-        <v>1.1204</v>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B1325" t="n">
+        <v>1348.5</v>
+      </c>
+      <c r="C1325" t="n">
+        <v>853.02</v>
+      </c>
+      <c r="D1325" t="n">
+        <v>1512.14</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="E1326" t="n">
-        <v>121.4048</v>
-      </c>
-      <c r="F1326" t="n">
-        <v>158</v>
-      </c>
-      <c r="G1326" t="n">
-        <v>1.1231</v>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1326" t="n">
+        <v>1342.4</v>
+      </c>
+      <c r="C1326" t="n">
+        <v>850.24</v>
+      </c>
+      <c r="D1326" t="n">
+        <v>1505.17</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1327" t="n">
+        <v>1332.1</v>
+      </c>
+      <c r="C1327" t="n">
+        <v>840.1799999999999</v>
+      </c>
+      <c r="D1327" t="n">
+        <v>1493.48</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B1328" t="n">
+        <v>1328</v>
+      </c>
+      <c r="C1328" t="n">
+        <v>839.0700000000001</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>1491.14</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1328"/>
+  <dimension ref="A1:G1331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32357,177 +32357,288 @@
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B1318" t="n">
-        <v>1358.5</v>
-      </c>
-      <c r="C1318" t="n">
-        <v>860.16</v>
-      </c>
-      <c r="D1318" t="n">
-        <v>1524.1</v>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E1318" t="n">
+        <v>121.2708</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>157.97</v>
+      </c>
+      <c r="G1318" t="n">
+        <v>1.1211</v>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B1319" t="n">
-        <v>1343.4</v>
+        <v>1358.5</v>
       </c>
       <c r="C1319" t="n">
-        <v>849.1</v>
+        <v>860.16</v>
       </c>
       <c r="D1319" t="n">
-        <v>1512.27</v>
+        <v>1524.1</v>
+      </c>
+      <c r="E1319" t="n">
+        <v>120.8976</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>158.12</v>
+      </c>
+      <c r="G1319" t="n">
+        <v>1.1262</v>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>1339.2</v>
+        <v>1343.4</v>
       </c>
       <c r="C1320" t="n">
-        <v>847.46</v>
+        <v>849.1</v>
       </c>
       <c r="D1320" t="n">
-        <v>1500.04</v>
+        <v>1512.27</v>
+      </c>
+      <c r="E1320" t="n">
+        <v>121.2558</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>158.11</v>
+      </c>
+      <c r="G1320" t="n">
+        <v>1.1187</v>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B1321" t="n">
-        <v>1338</v>
+        <v>1339.2</v>
       </c>
       <c r="C1321" t="n">
-        <v>845.42</v>
+        <v>847.46</v>
       </c>
       <c r="D1321" t="n">
-        <v>1498.43</v>
+        <v>1500.04</v>
+      </c>
+      <c r="E1321" t="n">
+        <v>121.4469</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>158.33</v>
+      </c>
+      <c r="G1321" t="n">
+        <v>1.1192</v>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B1322" t="n">
-        <v>1335.8</v>
-      </c>
-      <c r="C1322" t="n">
-        <v>842.3</v>
-      </c>
-      <c r="D1322" t="n">
-        <v>1490.42</v>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E1322" t="n">
+        <v>121.6023</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>158.34</v>
+      </c>
+      <c r="G1322" t="n">
+        <v>1.1193</v>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B1323" t="n">
-        <v>1340.5</v>
+        <v>1338</v>
       </c>
       <c r="C1323" t="n">
-        <v>846.5700000000001</v>
+        <v>845.42</v>
       </c>
       <c r="D1323" t="n">
-        <v>1500.96</v>
+        <v>1498.43</v>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B1324" t="n">
-        <v>1338.6</v>
+        <v>1335.8</v>
       </c>
       <c r="C1324" t="n">
-        <v>846.65</v>
+        <v>842.3</v>
       </c>
       <c r="D1324" t="n">
-        <v>1495.48</v>
+        <v>1490.42</v>
+      </c>
+      <c r="E1324" t="n">
+        <v>121.4433</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>158.36</v>
+      </c>
+      <c r="G1324" t="n">
+        <v>1.1196</v>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B1325" t="n">
-        <v>1348.5</v>
+        <v>1340.5</v>
       </c>
       <c r="C1325" t="n">
-        <v>853.02</v>
+        <v>846.5700000000001</v>
       </c>
       <c r="D1325" t="n">
-        <v>1512.14</v>
+        <v>1500.96</v>
+      </c>
+      <c r="E1325" t="n">
+        <v>122.0037</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>158.84</v>
+      </c>
+      <c r="G1325" t="n">
+        <v>1.1123</v>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B1326" t="n">
-        <v>1342.4</v>
+        <v>1338.6</v>
       </c>
       <c r="C1326" t="n">
-        <v>850.24</v>
+        <v>846.65</v>
       </c>
       <c r="D1326" t="n">
-        <v>1505.17</v>
+        <v>1495.48</v>
+      </c>
+      <c r="E1326" t="n">
+        <v>121.5693</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>158.18</v>
+      </c>
+      <c r="G1326" t="n">
+        <v>1.1204</v>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B1327" t="n">
-        <v>1332.1</v>
+        <v>1348.5</v>
       </c>
       <c r="C1327" t="n">
-        <v>840.1799999999999</v>
+        <v>853.02</v>
       </c>
       <c r="D1327" t="n">
-        <v>1493.48</v>
+        <v>1512.14</v>
+      </c>
+      <c r="E1327" t="n">
+        <v>121.4048</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>158</v>
+      </c>
+      <c r="G1327" t="n">
+        <v>1.1231</v>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B1328" t="n">
+        <v>1342.4</v>
+      </c>
+      <c r="C1328" t="n">
+        <v>850.24</v>
+      </c>
+      <c r="D1328" t="n">
+        <v>1505.17</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B1329" t="n">
+        <v>1332.1</v>
+      </c>
+      <c r="C1329" t="n">
+        <v>840.1799999999999</v>
+      </c>
+      <c r="D1329" t="n">
+        <v>1493.48</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B1328" t="n">
+      <c r="B1330" t="n">
         <v>1328</v>
       </c>
-      <c r="C1328" t="n">
+      <c r="C1330" t="n">
         <v>839.0700000000001</v>
       </c>
-      <c r="D1328" t="n">
+      <c r="D1330" t="n">
         <v>1491.14</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B1331" t="n">
+        <v>1325.5</v>
+      </c>
+      <c r="C1331" t="n">
+        <v>838.26</v>
+      </c>
+      <c r="D1331" t="n">
+        <v>1488.6</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1331"/>
+  <dimension ref="A1:G1332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32641,6 +32641,22 @@
         <v>1488.6</v>
       </c>
     </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B1332" t="n">
+        <v>1324.6</v>
+      </c>
+      <c r="C1332" t="n">
+        <v>846.12</v>
+      </c>
+      <c r="D1332" t="n">
+        <v>1486.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1332"/>
+  <dimension ref="A1:G1334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32592,6 +32592,15 @@
       <c r="D1328" t="n">
         <v>1505.17</v>
       </c>
+      <c r="E1328" t="n">
+        <v>121.3248</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>158.49</v>
+      </c>
+      <c r="G1328" t="n">
+        <v>1.1209</v>
+      </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
@@ -32608,6 +32617,15 @@
       <c r="D1329" t="n">
         <v>1493.48</v>
       </c>
+      <c r="E1329" t="n">
+        <v>121.116</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>158.2</v>
+      </c>
+      <c r="G1329" t="n">
+        <v>1.1232</v>
+      </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
@@ -32624,6 +32642,15 @@
       <c r="D1330" t="n">
         <v>1491.14</v>
       </c>
+      <c r="E1330" t="n">
+        <v>121.3422</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>158.13</v>
+      </c>
+      <c r="G1330" t="n">
+        <v>1.1219</v>
+      </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
@@ -32640,6 +32667,15 @@
       <c r="D1331" t="n">
         <v>1488.6</v>
       </c>
+      <c r="E1331" t="n">
+        <v>121.3531</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>157.11</v>
+      </c>
+      <c r="G1331" t="n">
+        <v>1.1212</v>
+      </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
@@ -32655,6 +32691,47 @@
       </c>
       <c r="D1332" t="n">
         <v>1486.4</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>121.3202</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>156.87</v>
+      </c>
+      <c r="G1332" t="n">
+        <v>1.1199</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B1333" t="n">
+        <v>1324.3</v>
+      </c>
+      <c r="C1333" t="n">
+        <v>843.83</v>
+      </c>
+      <c r="D1333" t="n">
+        <v>1483.81</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B1334" t="n">
+        <v>1322.6</v>
+      </c>
+      <c r="C1334" t="n">
+        <v>839.83</v>
+      </c>
+      <c r="D1334" t="n">
+        <v>1477.87</v>
       </c>
     </row>
   </sheetData>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1334"/>
+  <dimension ref="A1:G1335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32734,6 +32734,22 @@
         <v>1477.87</v>
       </c>
     </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B1335" t="n">
+        <v>1324.3</v>
+      </c>
+      <c r="C1335" t="n">
+        <v>838.3</v>
+      </c>
+      <c r="D1335" t="n">
+        <v>1473.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1335"/>
+  <dimension ref="A1:G1336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32750,6 +32750,22 @@
         <v>1473.81</v>
       </c>
     </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B1336" t="n">
+        <v>1336.3</v>
+      </c>
+      <c r="C1336" t="n">
+        <v>846.89</v>
+      </c>
+      <c r="D1336" t="n">
+        <v>1490.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/fx_daily.xlsx
+++ b/site/data/downloads/fx_daily.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1336"/>
+  <dimension ref="A1:G1337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -32766,6 +32766,22 @@
         <v>1490.51</v>
       </c>
     </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B1337" t="n">
+        <v>1335.3</v>
+      </c>
+      <c r="C1337" t="n">
+        <v>846.41</v>
+      </c>
+      <c r="D1337" t="n">
+        <v>1494</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
